--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,309 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131340655</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90850</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>889</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Plicatura pendula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Haknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>651919</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6621827</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131340642</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Haknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>651919</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6621824</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131340463</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Haknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>651766</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6621762</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131340655</v>
       </c>
       <c r="B3" t="n">
-        <v>90850</v>
+        <v>90851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131340642</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131340463</v>
       </c>
       <c r="B5" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131340655</v>
       </c>
       <c r="B3" t="n">
-        <v>90851</v>
+        <v>90853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131340642</v>
       </c>
       <c r="B4" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131340463</v>
       </c>
       <c r="B5" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131340655</v>
       </c>
       <c r="B3" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131340642</v>
       </c>
       <c r="B4" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131340463</v>
       </c>
       <c r="B5" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131340655</v>
       </c>
       <c r="B3" t="n">
-        <v>90854</v>
+        <v>90855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131340642</v>
       </c>
       <c r="B4" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131340463</v>
       </c>
       <c r="B5" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131340655</v>
       </c>
       <c r="B3" t="n">
-        <v>90855</v>
+        <v>90858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131340642</v>
       </c>
       <c r="B4" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131340463</v>
       </c>
       <c r="B5" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131340655</v>
       </c>
       <c r="B3" t="n">
-        <v>90858</v>
+        <v>90859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131340642</v>
       </c>
       <c r="B4" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131340463</v>
       </c>
       <c r="B5" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131340655</v>
       </c>
       <c r="B3" t="n">
-        <v>90859</v>
+        <v>90865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131340642</v>
       </c>
       <c r="B4" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131340463</v>
       </c>
       <c r="B5" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131340655</v>
       </c>
       <c r="B3" t="n">
-        <v>90865</v>
+        <v>90866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131340642</v>
       </c>
       <c r="B4" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131340463</v>
       </c>
       <c r="B5" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131340655</v>
       </c>
       <c r="B3" t="n">
-        <v>90866</v>
+        <v>90869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131340642</v>
       </c>
       <c r="B4" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131340463</v>
       </c>
       <c r="B5" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131340655</v>
       </c>
       <c r="B3" t="n">
-        <v>90869</v>
+        <v>90875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131340642</v>
       </c>
       <c r="B4" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131340463</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93292199</v>
+        <v>99191172</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -716,17 +711,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällmark, Nyborg, Upl</t>
+          <t>Vassunda-Örby, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>652390.8230263025</v>
+        <v>652410</v>
       </c>
       <c r="R2" t="n">
-        <v>6621818.84179996</v>
+        <v>6621980</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2022-03-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2022-03-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +790,7 @@
         <v>131340655</v>
       </c>
       <c r="B3" t="n">
-        <v>90875</v>
+        <v>90946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131340642</v>
+        <v>131340463</v>
       </c>
       <c r="B4" t="n">
-        <v>91859</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651919</v>
+        <v>651766</v>
       </c>
       <c r="R4" t="n">
-        <v>6621824</v>
+        <v>6621762</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131340463</v>
+        <v>93291725</v>
       </c>
       <c r="B5" t="n">
-        <v>91838</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,37 +1000,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Haknäs, Upl</t>
+          <t>Hällmark, Nyborg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651766</v>
+        <v>652365</v>
       </c>
       <c r="R5" t="n">
-        <v>6621762</v>
+        <v>6621861</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,12 +1064,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,22 +1088,1697 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Hällmarksmosaik med tall</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96815812</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vassunda-Örby, Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>652235</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6621815</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-10-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-10-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97314486</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lavfältet, Vassunda, Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>652478</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6621866</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-11-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>99569594</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>652478</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6621851</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>93292199</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hällmark, Nyborg, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>652391</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6621819</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131340642</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Haknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>651919</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6621824</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Carin von Köhler</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Carin von Köhler</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131666859</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nyborg, Vassunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>652440</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6621928</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131666936</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nyborg, Vassunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>652377</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6621812</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104473266</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vassunda-Örby, Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>651841</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6621746</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>119788010</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skjurvilan, Skjurvilan, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>652046</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6622341</v>
+      </c>
+      <c r="S14" t="n">
+        <v>16</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118088239</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Edsberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>651419</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6621818</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131340377</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Haknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>651575</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6621779</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131340405</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Haknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>651577</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6621779</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131340419</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Haknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>651583</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6621778</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131340428</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Haknäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>651595</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6621774</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>101865747</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>651569</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6621784</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vassunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-06-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-06-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Robert Hagblom</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Robert Hagblom</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2214-2026 artfynd.xlsx
+++ b/artfynd/A 2214-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99191172</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131340655</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131340463</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93291725</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96815812</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97314486</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99569594</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93292199</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1658,6 +1703,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131340642</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1763,6 +1813,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131666859</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1872,6 +1927,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131666936</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1989,6 +2049,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104473266</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,6 +2172,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119788010</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2230,6 +2300,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118088239</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2340,6 +2415,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131340377</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2450,6 +2530,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131340405</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2560,6 +2645,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131340419</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2670,6 +2760,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131340428</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2779,8 +2874,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101865747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>